--- a/assets/data/tkb-giao-vien.xlsx
+++ b/assets/data/tkb-giao-vien.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NH 2026 2027\TKB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NH 2026 2027\TKB\Web\smart-timetable-v2.3\smart-timetable-v2\assets\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39F700F5-7DF9-48BC-90FE-3742AB732397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DC6B6E-A6F5-447B-AF9C-062160FC9DA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="." sheetId="10" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511" iterateCount="1"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="449">
   <si>
     <t>Trường</t>
   </si>
@@ -1116,18 +1116,12 @@
     <t>10A3 - GDTC</t>
   </si>
   <si>
-    <t>11B5 - GDQP</t>
-  </si>
-  <si>
     <t>11B10 - GDQP</t>
   </si>
   <si>
     <t>11B4 - GDQP</t>
   </si>
   <si>
-    <t>11B3 - GDQP</t>
-  </si>
-  <si>
     <t>12C8 - GDTC</t>
   </si>
   <si>
@@ -1137,18 +1131,12 @@
     <t>12C10 - GDTC</t>
   </si>
   <si>
-    <t>11B7 - GDQP</t>
-  </si>
-  <si>
     <t>11B1 - GDTC</t>
   </si>
   <si>
     <t>11B2 - GDTC</t>
   </si>
   <si>
-    <t>12C1 - GDTC</t>
-  </si>
-  <si>
     <t>12C2 - GDTC</t>
   </si>
   <si>
@@ -1203,9 +1191,6 @@
     <t>10A10 - GDTC</t>
   </si>
   <si>
-    <t>12C5 - GDQP</t>
-  </si>
-  <si>
     <t>12C6 - GDQP</t>
   </si>
   <si>
@@ -1296,9 +1281,6 @@
     <t>12C3 - GDQP</t>
   </si>
   <si>
-    <t>12C7 - GDQP</t>
-  </si>
-  <si>
     <t>Tuần 7- Áp dụng từ ngày 19.10.2026</t>
   </si>
   <si>
@@ -1317,9 +1299,6 @@
     <t>12C1 - GDQP</t>
   </si>
   <si>
-    <t>12C8 - GDQP</t>
-  </si>
-  <si>
     <t>12C3 - GDĐP</t>
   </si>
   <si>
@@ -1345,6 +1324,54 @@
   </si>
   <si>
     <t>12C10 - GDQP</t>
+  </si>
+  <si>
+    <t>11B10 - GDĐP</t>
+  </si>
+  <si>
+    <t>12C5 - GDĐP</t>
+  </si>
+  <si>
+    <t>Nguyễn Thị Nhung NN</t>
+  </si>
+  <si>
+    <t>11B4 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>11B10 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>11B9 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>12C7 - AI</t>
+  </si>
+  <si>
+    <t>11B2 - GDĐP</t>
+  </si>
+  <si>
+    <t>10A1 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>12C5 - AI</t>
+  </si>
+  <si>
+    <t>12C7 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>10A6 - GDQP</t>
+  </si>
+  <si>
+    <t>10A9 - GDQP</t>
+  </si>
+  <si>
+    <t>10A3 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>10A5 - HĐTN HN</t>
+  </si>
+  <si>
+    <t>10A10 - HĐTN HN</t>
   </si>
 </sst>
 </file>
@@ -4147,7 +4174,7 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="99" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="G1" s="99"/>
       <c r="H1" s="99"/>
@@ -4257,7 +4284,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="100" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="J4" s="100"/>
       <c r="K4" s="100"/>
@@ -4508,7 +4535,9 @@
       <c r="K9" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="36" t="s">
+        <v>104</v>
+      </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13"/>
@@ -4527,9 +4556,11 @@
       <c r="Z9" s="42"/>
       <c r="AA9" s="36"/>
       <c r="AB9" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="AC9" s="13"/>
+        <v>105</v>
+      </c>
+      <c r="AC9" s="13" t="s">
+        <v>105</v>
+      </c>
       <c r="AD9" s="13"/>
       <c r="AE9" s="37"/>
     </row>
@@ -4556,7 +4587,7 @@
         <v>106</v>
       </c>
       <c r="N10" s="13" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="O10" s="13"/>
       <c r="P10" s="37"/>
@@ -4566,20 +4597,22 @@
       </c>
       <c r="S10" s="13"/>
       <c r="T10" s="13" t="s">
-        <v>431</v>
+        <v>424</v>
       </c>
       <c r="U10" s="71" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="V10" s="36"/>
       <c r="W10" s="13"/>
       <c r="X10" s="13" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="Y10" s="13" t="s">
         <v>106</v>
       </c>
-      <c r="Z10" s="37"/>
+      <c r="Z10" s="37" t="s">
+        <v>424</v>
+      </c>
       <c r="AA10" s="36"/>
       <c r="AB10" s="13"/>
       <c r="AC10" s="13"/>
@@ -4607,16 +4640,16 @@
         <v>111</v>
       </c>
       <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="37" t="s">
-        <v>412</v>
-      </c>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="13" t="s">
-        <v>111</v>
-      </c>
+      <c r="O11" s="13" t="s">
+        <v>407</v>
+      </c>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="36" t="s">
+        <v>118</v>
+      </c>
+      <c r="R11" s="13"/>
       <c r="S11" s="13" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="T11" s="13" t="s">
         <v>107</v>
@@ -4629,14 +4662,12 @@
       </c>
       <c r="W11" s="13"/>
       <c r="X11" s="13" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="Y11" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="Z11" s="37" t="s">
-        <v>118</v>
-      </c>
+      <c r="Z11" s="37"/>
       <c r="AA11" s="36" t="s">
         <v>107</v>
       </c>
@@ -4644,7 +4675,7 @@
         <v>107</v>
       </c>
       <c r="AC11" s="13" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="AD11" s="13" t="s">
         <v>103</v>
@@ -4685,16 +4716,16 @@
       <c r="Y12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="Z12" s="37" t="s">
-        <v>108</v>
-      </c>
+      <c r="Z12" s="37"/>
       <c r="AA12" s="36"/>
       <c r="AB12" s="13"/>
       <c r="AC12" s="13"/>
       <c r="AD12" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="AE12" s="37"/>
+      <c r="AE12" s="37" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="13" spans="1:31" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="31" t="s">
@@ -4714,10 +4745,10 @@
       <c r="I13" s="12"/>
       <c r="J13" s="12"/>
       <c r="K13" s="41"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="13" t="s">
+      <c r="L13" s="36" t="s">
         <v>109</v>
       </c>
+      <c r="M13" s="13"/>
       <c r="N13" s="13" t="s">
         <v>102</v>
       </c>
@@ -4728,24 +4759,24 @@
       <c r="Q13" s="36" t="s">
         <v>115</v>
       </c>
-      <c r="R13" s="13"/>
+      <c r="R13" s="13" t="s">
+        <v>102</v>
+      </c>
       <c r="S13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="T13" s="13"/>
+      <c r="T13" s="13" t="s">
+        <v>113</v>
+      </c>
       <c r="U13" s="71"/>
-      <c r="V13" s="36" t="s">
+      <c r="V13" s="36"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="W13" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="X13" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="Y13" s="13"/>
       <c r="Z13" s="37" t="s">
-        <v>102</v>
+        <v>114</v>
       </c>
       <c r="AA13" s="36" t="s">
         <v>110</v>
@@ -4754,8 +4785,12 @@
       <c r="AC13" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="AD13" s="13"/>
-      <c r="AE13" s="37"/>
+      <c r="AD13" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="AE13" s="37" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="14" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="31" t="s">
@@ -4767,25 +4802,23 @@
         <v>117</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="F14" s="37" t="s">
         <v>119</v>
       </c>
       <c r="G14" s="40" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12"/>
       <c r="J14" s="12" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="K14" s="41" t="s">
-        <v>396</v>
-      </c>
-      <c r="L14" s="36" t="s">
-        <v>117</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="L14" s="36"/>
       <c r="M14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
@@ -4794,7 +4827,7 @@
       <c r="R14" s="13"/>
       <c r="S14" s="13"/>
       <c r="T14" s="13" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="U14" s="71" t="s">
         <v>117</v>
@@ -4806,7 +4839,7 @@
         <v>116</v>
       </c>
       <c r="X14" s="13" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="Y14" s="13"/>
       <c r="Z14" s="37"/>
@@ -4815,10 +4848,12 @@
       </c>
       <c r="AB14" s="13"/>
       <c r="AC14" s="13" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AD14" s="13"/>
-      <c r="AE14" s="37"/>
+      <c r="AE14" s="37" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="15" spans="1:31" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="31" t="s">
@@ -4838,14 +4873,12 @@
       <c r="I15" s="12"/>
       <c r="J15" s="12"/>
       <c r="K15" s="41"/>
-      <c r="L15" s="36" t="s">
+      <c r="L15" s="36"/>
+      <c r="M15" s="13"/>
+      <c r="N15" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13" t="s">
-        <v>120</v>
-      </c>
+      <c r="O15" s="13"/>
       <c r="P15" s="37" t="s">
         <v>124</v>
       </c>
@@ -4853,25 +4886,31 @@
       <c r="R15" s="13"/>
       <c r="S15" s="13"/>
       <c r="T15" s="13"/>
-      <c r="U15" s="71"/>
-      <c r="V15" s="36" t="s">
-        <v>122</v>
-      </c>
-      <c r="W15" s="13" t="s">
+      <c r="U15" s="71" t="s">
         <v>120</v>
       </c>
+      <c r="V15" s="36"/>
+      <c r="W15" s="13"/>
       <c r="X15" s="13"/>
       <c r="Y15" s="13"/>
-      <c r="Z15" s="37"/>
+      <c r="Z15" s="37" t="s">
+        <v>122</v>
+      </c>
       <c r="AA15" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="AB15" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC15" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="AD15" s="13" t="s">
+        <v>433</v>
+      </c>
+      <c r="AE15" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE15" s="37"/>
     </row>
     <row r="16" spans="1:31" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="31" t="s">
@@ -4887,8 +4926,12 @@
       <c r="I16" s="11"/>
       <c r="J16" s="11"/>
       <c r="K16" s="41"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="10"/>
+      <c r="L16" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>153</v>
+      </c>
       <c r="N16" s="10"/>
       <c r="O16" s="13"/>
       <c r="P16" s="37"/>
@@ -4932,11 +4975,11 @@
       <c r="M17" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="N17" s="13"/>
+      <c r="N17" s="13" t="s">
+        <v>126</v>
+      </c>
       <c r="O17" s="13"/>
-      <c r="P17" s="37" t="s">
-        <v>126</v>
-      </c>
+      <c r="P17" s="37"/>
       <c r="Q17" s="36"/>
       <c r="R17" s="13" t="s">
         <v>126</v>
@@ -4945,9 +4988,11 @@
         <v>126</v>
       </c>
       <c r="T17" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="U17" s="71"/>
+        <v>408</v>
+      </c>
+      <c r="U17" s="71" t="s">
+        <v>408</v>
+      </c>
       <c r="V17" s="36"/>
       <c r="W17" s="13"/>
       <c r="X17" s="13"/>
@@ -5002,9 +5047,7 @@
       <c r="V18" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="W18" s="13" t="s">
-        <v>159</v>
-      </c>
+      <c r="W18" s="13"/>
       <c r="X18" s="13" t="s">
         <v>130</v>
       </c>
@@ -5024,7 +5067,9 @@
       <c r="AD18" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="AE18" s="37"/>
+      <c r="AE18" s="37" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="19" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
@@ -5047,33 +5092,31 @@
       <c r="N19" s="13"/>
       <c r="O19" s="13"/>
       <c r="P19" s="37"/>
-      <c r="Q19" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="R19" s="13" t="s">
-        <v>134</v>
-      </c>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="13"/>
       <c r="S19" s="13"/>
-      <c r="T19" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="U19" s="71" t="s">
-        <v>135</v>
-      </c>
+      <c r="T19" s="13"/>
+      <c r="U19" s="71"/>
       <c r="V19" s="36"/>
       <c r="W19" s="13"/>
       <c r="X19" s="13"/>
       <c r="Y19" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="Z19" s="37"/>
+      <c r="Z19" s="37" t="s">
+        <v>135</v>
+      </c>
       <c r="AA19" s="36"/>
       <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
+      <c r="AC19" s="13" t="s">
+        <v>135</v>
+      </c>
       <c r="AD19" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AE19" s="37"/>
+      <c r="AE19" s="37" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="20" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
@@ -5106,9 +5149,7 @@
         <v>141</v>
       </c>
       <c r="N20" s="13"/>
-      <c r="O20" s="13" t="s">
-        <v>140</v>
-      </c>
+      <c r="O20" s="13"/>
       <c r="P20" s="37"/>
       <c r="Q20" s="36"/>
       <c r="R20" s="13"/>
@@ -5126,17 +5167,19 @@
       <c r="Z20" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="AA20" s="36"/>
+      <c r="AA20" s="36" t="s">
+        <v>138</v>
+      </c>
       <c r="AB20" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="AC20" s="13" t="s">
-        <v>138</v>
-      </c>
+      <c r="AC20" s="13"/>
       <c r="AD20" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="AE20" s="37"/>
+      <c r="AE20" s="37" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="21" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="31" t="s">
@@ -5157,29 +5200,27 @@
       <c r="N21" s="13"/>
       <c r="O21" s="13"/>
       <c r="P21" s="37"/>
-      <c r="Q21" s="36"/>
+      <c r="Q21" s="36" t="s">
+        <v>142</v>
+      </c>
       <c r="R21" s="13"/>
       <c r="S21" s="13" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="T21" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="U21" s="71" t="s">
-        <v>146</v>
-      </c>
+      <c r="U21" s="71"/>
       <c r="V21" s="36" t="s">
         <v>155</v>
       </c>
       <c r="W21" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="X21" s="13" t="s">
-        <v>146</v>
-      </c>
+      <c r="X21" s="13"/>
       <c r="Y21" s="13"/>
       <c r="Z21" s="37" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="AA21" s="36"/>
       <c r="AB21" s="13" t="s">
@@ -5191,7 +5232,9 @@
       <c r="AD21" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="AE21" s="37"/>
+      <c r="AE21" s="37" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="22" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="31" t="s">
@@ -5224,20 +5267,18 @@
       <c r="P22" s="37" t="s">
         <v>148</v>
       </c>
-      <c r="Q22" s="36" t="s">
-        <v>149</v>
-      </c>
-      <c r="R22" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="S22" s="10" t="s">
-        <v>148</v>
-      </c>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="13"/>
+      <c r="S22" s="10"/>
       <c r="T22" s="10"/>
       <c r="U22" s="71"/>
       <c r="V22" s="36"/>
-      <c r="W22" s="13"/>
-      <c r="X22" s="13"/>
+      <c r="W22" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="X22" s="13" t="s">
+        <v>149</v>
+      </c>
       <c r="Y22" s="10" t="s">
         <v>148</v>
       </c>
@@ -5364,11 +5405,9 @@
       <c r="M25" s="13" t="s">
         <v>153</v>
       </c>
-      <c r="N25" s="13" t="s">
+      <c r="N25" s="13"/>
+      <c r="O25" s="13" t="s">
         <v>144</v>
-      </c>
-      <c r="O25" s="13" t="s">
-        <v>143</v>
       </c>
       <c r="P25" s="37" t="s">
         <v>143</v>
@@ -5376,18 +5415,18 @@
       <c r="Q25" s="36"/>
       <c r="R25" s="13"/>
       <c r="S25" s="13"/>
-      <c r="T25" s="13" t="s">
-        <v>143</v>
-      </c>
+      <c r="T25" s="13"/>
       <c r="U25" s="71"/>
       <c r="V25" s="36" t="s">
         <v>153</v>
       </c>
-      <c r="W25" s="13"/>
-      <c r="X25" s="13"/>
-      <c r="Y25" s="13" t="s">
-        <v>144</v>
-      </c>
+      <c r="W25" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="X25" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y25" s="13"/>
       <c r="Z25" s="37" t="s">
         <v>144</v>
       </c>
@@ -5395,7 +5434,9 @@
       <c r="AB25" s="13"/>
       <c r="AC25" s="13"/>
       <c r="AD25" s="13"/>
-      <c r="AE25" s="37"/>
+      <c r="AE25" s="37" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="26" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="31" t="s">
@@ -5419,29 +5460,21 @@
       <c r="K26" s="41" t="s">
         <v>160</v>
       </c>
-      <c r="L26" s="36" t="s">
-        <v>157</v>
-      </c>
+      <c r="L26" s="36"/>
       <c r="M26" s="13"/>
       <c r="N26" s="13" t="s">
         <v>132</v>
       </c>
       <c r="O26" s="13" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="P26" s="37" t="s">
         <v>158</v>
       </c>
       <c r="Q26" s="36"/>
-      <c r="R26" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="S26" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="T26" s="13" t="s">
-        <v>156</v>
-      </c>
+      <c r="R26" s="13"/>
+      <c r="S26" s="13"/>
+      <c r="T26" s="13"/>
       <c r="U26" s="71"/>
       <c r="V26" s="36" t="s">
         <v>158</v>
@@ -5456,7 +5489,7 @@
         <v>132</v>
       </c>
       <c r="Z26" s="37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AA26" s="36"/>
       <c r="AB26" s="13"/>
@@ -5526,22 +5559,20 @@
         <v>133</v>
       </c>
       <c r="L28" s="36"/>
-      <c r="M28" s="13" t="s">
+      <c r="M28" s="13"/>
+      <c r="N28" s="13"/>
+      <c r="O28" s="13"/>
+      <c r="P28" s="37" t="s">
         <v>136</v>
       </c>
-      <c r="N28" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="O28" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="P28" s="37"/>
       <c r="Q28" s="36"/>
       <c r="R28" s="13"/>
       <c r="S28" s="13"/>
       <c r="T28" s="13"/>
       <c r="U28" s="71"/>
-      <c r="V28" s="36"/>
+      <c r="V28" s="36" t="s">
+        <v>128</v>
+      </c>
       <c r="W28" s="13" t="s">
         <v>128</v>
       </c>
@@ -5549,9 +5580,11 @@
         <v>136</v>
       </c>
       <c r="Y28" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z28" s="37" t="s">
         <v>154</v>
       </c>
-      <c r="Z28" s="37"/>
       <c r="AA28" s="36"/>
       <c r="AB28" s="13"/>
       <c r="AC28" s="13"/>
@@ -5576,17 +5609,17 @@
       <c r="I29" s="12"/>
       <c r="J29" s="12"/>
       <c r="K29" s="37"/>
-      <c r="L29" s="64"/>
+      <c r="L29" s="64" t="s">
+        <v>167</v>
+      </c>
       <c r="M29" s="13" t="s">
         <v>164</v>
       </c>
       <c r="N29" s="13" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="O29" s="13"/>
-      <c r="P29" s="37" t="s">
-        <v>167</v>
-      </c>
+      <c r="P29" s="37"/>
       <c r="Q29" s="36"/>
       <c r="R29" s="11" t="s">
         <v>167</v>
@@ -5594,7 +5627,9 @@
       <c r="S29" s="13" t="s">
         <v>165</v>
       </c>
-      <c r="T29" s="13"/>
+      <c r="T29" s="13" t="s">
+        <v>162</v>
+      </c>
       <c r="U29" s="71"/>
       <c r="V29" s="36"/>
       <c r="W29" s="13"/>
@@ -5602,7 +5637,7 @@
         <v>162</v>
       </c>
       <c r="Y29" s="13" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="Z29" s="37" t="s">
         <v>165</v>
@@ -5610,16 +5645,16 @@
       <c r="AA29" s="36" t="s">
         <v>167</v>
       </c>
-      <c r="AB29" s="84" t="s">
-        <v>168</v>
-      </c>
+      <c r="AB29" s="84"/>
       <c r="AC29" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="AD29" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="AE29" s="66" t="s">
         <v>165</v>
       </c>
-      <c r="AD29" s="13" t="s">
-        <v>426</v>
-      </c>
-      <c r="AE29" s="66"/>
     </row>
     <row r="30" spans="1:32" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="31" t="s">
@@ -5651,9 +5686,7 @@
       <c r="S30" s="13" t="s">
         <v>171</v>
       </c>
-      <c r="T30" s="13" t="s">
-        <v>170</v>
-      </c>
+      <c r="T30" s="13"/>
       <c r="U30" s="71"/>
       <c r="V30" s="36"/>
       <c r="W30" s="13"/>
@@ -5666,7 +5699,9 @@
       <c r="AD30" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="AE30" s="37"/>
+      <c r="AE30" s="37" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="31" spans="1:32" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="31" t="s">
@@ -5688,12 +5723,16 @@
         <v>175</v>
       </c>
       <c r="L31" s="38"/>
-      <c r="M31" s="83"/>
+      <c r="M31" s="83" t="s">
+        <v>173</v>
+      </c>
       <c r="O31" s="17"/>
       <c r="P31" s="39"/>
       <c r="Q31" s="38"/>
       <c r="S31" s="83"/>
-      <c r="T31" s="17"/>
+      <c r="T31" s="17" t="s">
+        <v>174</v>
+      </c>
       <c r="U31" s="70" t="s">
         <v>174</v>
       </c>
@@ -5731,9 +5770,7 @@
       <c r="J32" s="12"/>
       <c r="K32" s="41"/>
       <c r="L32" s="40"/>
-      <c r="M32" s="17" t="s">
-        <v>173</v>
-      </c>
+      <c r="M32" s="17"/>
       <c r="N32" s="17"/>
       <c r="O32" s="16"/>
       <c r="P32" s="51"/>
@@ -5783,15 +5820,11 @@
       <c r="R33" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="S33" s="13" t="s">
-        <v>176</v>
-      </c>
+      <c r="S33" s="13"/>
       <c r="T33" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="U33" s="71" t="s">
-        <v>179</v>
-      </c>
+      <c r="U33" s="71"/>
       <c r="V33" s="36" t="s">
         <v>177</v>
       </c>
@@ -5800,9 +5833,7 @@
       <c r="Y33" s="13" t="s">
         <v>178</v>
       </c>
-      <c r="Z33" s="37" t="s">
-        <v>179</v>
-      </c>
+      <c r="Z33" s="37"/>
       <c r="AA33" s="36" t="s">
         <v>176</v>
       </c>
@@ -5856,7 +5887,7 @@
     </row>
     <row r="35" spans="1:32" ht="22.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="31" t="s">
-        <v>35</v>
+        <v>435</v>
       </c>
       <c r="B35" s="36"/>
       <c r="C35" s="13"/>
@@ -5874,13 +5905,13 @@
         <v>172</v>
       </c>
       <c r="K35" s="41"/>
-      <c r="L35" s="36"/>
+      <c r="L35" s="36" t="s">
+        <v>172</v>
+      </c>
       <c r="M35" s="13" t="s">
         <v>172</v>
       </c>
-      <c r="N35" s="13" t="s">
-        <v>172</v>
-      </c>
+      <c r="N35" s="13"/>
       <c r="O35" s="11"/>
       <c r="P35" s="37"/>
       <c r="Q35" s="36"/>
@@ -5914,22 +5945,18 @@
       <c r="I36" s="12"/>
       <c r="J36" s="12"/>
       <c r="K36" s="57"/>
-      <c r="L36" s="36" t="s">
-        <v>186</v>
-      </c>
+      <c r="L36" s="36"/>
       <c r="M36" s="13"/>
       <c r="N36" s="13"/>
       <c r="O36" s="13"/>
-      <c r="P36" s="37"/>
-      <c r="Q36" s="36" t="s">
+      <c r="P36" s="37" t="s">
         <v>186</v>
       </c>
+      <c r="Q36" s="36"/>
       <c r="R36" s="6"/>
       <c r="S36" s="10"/>
       <c r="T36" s="6"/>
-      <c r="U36" s="71" t="s">
-        <v>180</v>
-      </c>
+      <c r="U36" s="71"/>
       <c r="V36" s="64"/>
       <c r="W36" s="13"/>
       <c r="X36" s="13" t="s">
@@ -5938,20 +5965,22 @@
       <c r="Y36" s="13" t="s">
         <v>186</v>
       </c>
-      <c r="Z36" s="37"/>
+      <c r="Z36" s="37" t="s">
+        <v>186</v>
+      </c>
       <c r="AA36" s="36" t="s">
         <v>180</v>
       </c>
       <c r="AB36" s="13" t="s">
         <v>180</v>
       </c>
-      <c r="AC36" s="13" t="s">
-        <v>182</v>
-      </c>
+      <c r="AC36" s="13"/>
       <c r="AD36" s="13" t="s">
         <v>182</v>
       </c>
-      <c r="AE36" s="37"/>
+      <c r="AE36" s="37" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="37" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="31" t="s">
@@ -5975,9 +6004,7 @@
       <c r="K37" s="41" t="s">
         <v>188</v>
       </c>
-      <c r="L37" s="40" t="s">
-        <v>190</v>
-      </c>
+      <c r="L37" s="40"/>
       <c r="M37" s="13"/>
       <c r="N37" s="13"/>
       <c r="O37" s="13" t="s">
@@ -5994,16 +6021,18 @@
         <v>189</v>
       </c>
       <c r="V37" s="36"/>
-      <c r="W37" s="13"/>
+      <c r="W37" s="13" t="s">
+        <v>425</v>
+      </c>
       <c r="X37" s="13" t="s">
         <v>189</v>
       </c>
       <c r="Y37" s="13"/>
-      <c r="Z37" s="37"/>
+      <c r="Z37" s="37" t="s">
+        <v>190</v>
+      </c>
       <c r="AA37" s="36"/>
-      <c r="AB37" s="13" t="s">
-        <v>432</v>
-      </c>
+      <c r="AB37" s="13"/>
       <c r="AC37" s="13"/>
       <c r="AD37" s="13"/>
       <c r="AE37" s="37"/>
@@ -6035,17 +6064,17 @@
       <c r="P38" s="37"/>
       <c r="Q38" s="36"/>
       <c r="R38" s="13" t="s">
-        <v>433</v>
+        <v>426</v>
       </c>
       <c r="S38" s="13"/>
       <c r="T38" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="U38" s="71" t="s">
+      <c r="U38" s="71"/>
+      <c r="V38" s="36"/>
+      <c r="W38" s="13" t="s">
         <v>191</v>
       </c>
-      <c r="V38" s="36"/>
-      <c r="W38" s="13"/>
       <c r="X38" s="13" t="s">
         <v>181</v>
       </c>
@@ -6055,15 +6084,15 @@
         <v>181</v>
       </c>
       <c r="AB38" s="13" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="AC38" s="13" t="s">
         <v>192</v>
       </c>
-      <c r="AD38" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="AE38" s="37"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="37" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="39" spans="1:32" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="31" t="s">
@@ -6085,16 +6114,22 @@
         <v>183</v>
       </c>
       <c r="K39" s="41"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="10"/>
-      <c r="N39" s="13"/>
+      <c r="L39" s="36" t="s">
+        <v>389</v>
+      </c>
+      <c r="M39" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="N39" s="13" t="s">
+        <v>436</v>
+      </c>
       <c r="O39" s="52"/>
       <c r="P39" s="37"/>
       <c r="Q39" s="36" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="S39" s="13" t="s">
         <v>194</v>
@@ -6102,25 +6137,31 @@
       <c r="T39" s="13"/>
       <c r="U39" s="36"/>
       <c r="V39" s="36" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
-      <c r="Y39" s="13"/>
+      <c r="Y39" s="13" t="s">
+        <v>183</v>
+      </c>
       <c r="Z39" s="42" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="AA39" s="36" t="s">
-        <v>434</v>
-      </c>
-      <c r="AB39" s="10"/>
+        <v>427</v>
+      </c>
+      <c r="AB39" s="10" t="s">
+        <v>427</v>
+      </c>
       <c r="AC39" s="10" t="s">
-        <v>194</v>
+        <v>389</v>
       </c>
       <c r="AD39" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="AE39" s="37" t="s">
         <v>183</v>
       </c>
-      <c r="AE39" s="37"/>
     </row>
     <row r="40" spans="1:32" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="31" t="s">
@@ -6150,17 +6191,13 @@
       <c r="K40" s="41" t="s">
         <v>169</v>
       </c>
-      <c r="L40" s="64" t="s">
-        <v>169</v>
-      </c>
-      <c r="M40" s="13" t="s">
+      <c r="L40" s="64"/>
+      <c r="M40" s="13"/>
+      <c r="N40" s="18"/>
+      <c r="O40" s="13"/>
+      <c r="P40" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="N40" s="18" t="s">
-        <v>187</v>
-      </c>
-      <c r="O40" s="13"/>
-      <c r="P40" s="37"/>
       <c r="Q40" s="36"/>
       <c r="R40" s="13"/>
       <c r="S40" s="13"/>
@@ -6243,7 +6280,9 @@
       <c r="T42" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="U42" s="71"/>
+      <c r="U42" s="71" t="s">
+        <v>438</v>
+      </c>
       <c r="V42" s="36"/>
       <c r="W42" s="13"/>
       <c r="X42" s="13"/>
@@ -6269,7 +6308,7 @@
       <c r="G43" s="40"/>
       <c r="H43" s="12"/>
       <c r="I43" s="12" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="J43" s="12" t="s">
         <v>197</v>
@@ -6277,12 +6316,8 @@
       <c r="K43" s="41" t="s">
         <v>195</v>
       </c>
-      <c r="L43" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="M43" s="13" t="s">
-        <v>195</v>
-      </c>
+      <c r="L43" s="36"/>
+      <c r="M43" s="13"/>
       <c r="N43" s="13"/>
       <c r="O43" s="13" t="s">
         <v>197</v>
@@ -6293,12 +6328,8 @@
       <c r="Q43" s="36"/>
       <c r="R43" s="13"/>
       <c r="S43" s="13"/>
-      <c r="T43" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="U43" s="71" t="s">
-        <v>197</v>
-      </c>
+      <c r="T43" s="13"/>
+      <c r="U43" s="71"/>
       <c r="V43" s="36"/>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
@@ -6326,12 +6357,12 @@
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
       <c r="K44" s="41"/>
-      <c r="L44" s="36"/>
+      <c r="L44" s="36" t="s">
+        <v>199</v>
+      </c>
       <c r="M44" s="13"/>
       <c r="N44" s="13"/>
-      <c r="O44" s="13" t="s">
-        <v>435</v>
-      </c>
+      <c r="O44" s="13"/>
       <c r="P44" s="37" t="s">
         <v>198</v>
       </c>
@@ -6341,7 +6372,9 @@
       <c r="R44" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="S44" s="13"/>
+      <c r="S44" s="13" t="s">
+        <v>428</v>
+      </c>
       <c r="T44" s="13"/>
       <c r="U44" s="71"/>
       <c r="V44" s="36"/>
@@ -6349,13 +6382,11 @@
       <c r="X44" s="13"/>
       <c r="Y44" s="13"/>
       <c r="Z44" s="37"/>
-      <c r="AA44" s="36"/>
-      <c r="AB44" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="AC44" s="13" t="s">
-        <v>199</v>
-      </c>
+      <c r="AA44" s="36" t="s">
+        <v>439</v>
+      </c>
+      <c r="AB44" s="13"/>
+      <c r="AC44" s="13"/>
       <c r="AD44" s="13"/>
       <c r="AE44" s="37"/>
     </row>
@@ -6398,31 +6429,39 @@
       <c r="R45" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="S45" s="13"/>
-      <c r="T45" s="13"/>
-      <c r="U45" s="71"/>
-      <c r="V45" s="36"/>
+      <c r="S45" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="T45" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="U45" s="71" t="s">
+        <v>200</v>
+      </c>
+      <c r="V45" s="36" t="s">
+        <v>203</v>
+      </c>
       <c r="W45" s="13"/>
       <c r="X45" s="13" t="s">
         <v>200</v>
       </c>
       <c r="Y45" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z45" s="37" t="s">
-        <v>202</v>
-      </c>
-      <c r="AA45" s="36"/>
+        <v>220</v>
+      </c>
+      <c r="Z45" s="37"/>
+      <c r="AA45" s="36" t="s">
+        <v>221</v>
+      </c>
       <c r="AB45" s="13" t="s">
         <v>200</v>
       </c>
       <c r="AC45" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="AD45" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="AE45" s="37"/>
+      <c r="AD45" s="13"/>
+      <c r="AE45" s="37" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="46" spans="1:32" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="31" t="s">
@@ -6448,15 +6487,15 @@
       <c r="K46" s="41" t="s">
         <v>206</v>
       </c>
-      <c r="L46" s="36"/>
+      <c r="L46" s="36" t="s">
+        <v>204</v>
+      </c>
       <c r="M46" s="13"/>
       <c r="N46" s="13" t="s">
         <v>184</v>
       </c>
       <c r="O46" s="13"/>
-      <c r="P46" s="37" t="s">
-        <v>204</v>
-      </c>
+      <c r="P46" s="37"/>
       <c r="Q46" s="36"/>
       <c r="R46" s="13"/>
       <c r="S46" s="13"/>
@@ -6489,7 +6528,9 @@
         <v>218</v>
       </c>
       <c r="K47" s="41"/>
-      <c r="L47" s="36"/>
+      <c r="L47" s="36" t="s">
+        <v>218</v>
+      </c>
       <c r="M47" s="13"/>
       <c r="N47" s="13" t="s">
         <v>212</v>
@@ -6498,10 +6539,10 @@
         <v>212</v>
       </c>
       <c r="P47" s="37"/>
-      <c r="Q47" s="36" t="s">
+      <c r="Q47" s="36"/>
+      <c r="R47" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="R47" s="13"/>
       <c r="S47" s="13"/>
       <c r="T47" s="13"/>
       <c r="U47" s="71"/>
@@ -6549,10 +6590,10 @@
       <c r="P48" s="37"/>
       <c r="Q48" s="36"/>
       <c r="R48" s="13"/>
-      <c r="S48" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="T48" s="13"/>
+      <c r="S48" s="13"/>
+      <c r="T48" s="13" t="s">
+        <v>209</v>
+      </c>
       <c r="U48" s="71" t="s">
         <v>209</v>
       </c>
@@ -6560,7 +6601,7 @@
         <v>209</v>
       </c>
       <c r="W48" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="X48" s="13"/>
       <c r="Y48" s="13" t="s">
@@ -6577,7 +6618,9 @@
       <c r="AD48" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="AE48" s="37"/>
+      <c r="AE48" s="37" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="49" spans="1:31" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="31" t="s">
@@ -6601,36 +6644,36 @@
       <c r="M49" s="13"/>
       <c r="N49" s="13"/>
       <c r="O49" s="13" t="s">
+        <v>211</v>
+      </c>
+      <c r="P49" s="37" t="s">
         <v>210</v>
       </c>
-      <c r="P49" s="37"/>
       <c r="Q49" s="36"/>
       <c r="R49" s="13"/>
       <c r="S49" s="13"/>
       <c r="T49" s="13"/>
       <c r="U49" s="71"/>
-      <c r="V49" s="36" t="s">
-        <v>211</v>
-      </c>
+      <c r="V49" s="36"/>
       <c r="W49" s="13" t="s">
         <v>213</v>
       </c>
       <c r="X49" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="Y49" s="13"/>
-      <c r="Z49" s="37" t="s">
+      <c r="Y49" s="13" t="s">
         <v>210</v>
       </c>
+      <c r="Z49" s="37"/>
       <c r="AA49" s="36"/>
       <c r="AB49" s="13" t="s">
         <v>211</v>
       </c>
       <c r="AC49" s="13"/>
-      <c r="AD49" s="13" t="s">
-        <v>210</v>
-      </c>
-      <c r="AE49" s="37"/>
+      <c r="AD49" s="13"/>
+      <c r="AE49" s="37" t="s">
+        <v>213</v>
+      </c>
     </row>
     <row r="50" spans="1:31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="31" t="s">
@@ -6657,13 +6700,13 @@
       <c r="L50" s="36"/>
       <c r="M50" s="13"/>
       <c r="N50" s="13" t="s">
-        <v>436</v>
+        <v>429</v>
       </c>
       <c r="O50" s="13" t="s">
         <v>216</v>
       </c>
       <c r="P50" s="37" t="s">
-        <v>437</v>
+        <v>430</v>
       </c>
       <c r="Q50" s="40"/>
       <c r="R50" s="13"/>
@@ -6672,26 +6715,32 @@
       </c>
       <c r="T50" s="13"/>
       <c r="U50" s="71" t="s">
-        <v>217</v>
-      </c>
-      <c r="V50" s="36" t="s">
-        <v>217</v>
-      </c>
-      <c r="W50" s="13" t="s">
-        <v>215</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="V50" s="36"/>
+      <c r="W50" s="13"/>
       <c r="X50" s="13" t="s">
         <v>219</v>
       </c>
-      <c r="Y50" s="13"/>
+      <c r="Y50" s="13" t="s">
+        <v>217</v>
+      </c>
       <c r="Z50" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="AA50" s="36"/>
-      <c r="AB50" s="13"/>
-      <c r="AC50" s="13"/>
+      <c r="AA50" s="36" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB50" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC50" s="13" t="s">
+        <v>429</v>
+      </c>
       <c r="AD50" s="13"/>
-      <c r="AE50" s="37"/>
+      <c r="AE50" s="37" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="51" spans="1:31" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="31" t="s">
@@ -6744,48 +6793,54 @@
       <c r="I52" s="12"/>
       <c r="J52" s="12"/>
       <c r="K52" s="41" t="s">
-        <v>403</v>
-      </c>
-      <c r="L52" s="36" t="s">
-        <v>222</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="L52" s="36"/>
       <c r="M52" s="13"/>
-      <c r="N52" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="O52" s="13"/>
+      <c r="N52" s="13"/>
+      <c r="O52" s="13" t="s">
+        <v>396</v>
+      </c>
       <c r="P52" s="37" t="s">
-        <v>402</v>
-      </c>
-      <c r="Q52" s="36"/>
+        <v>399</v>
+      </c>
+      <c r="Q52" s="36" t="s">
+        <v>397</v>
+      </c>
       <c r="R52" s="13" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="S52" s="13"/>
       <c r="T52" s="13" t="s">
-        <v>400</v>
+        <v>222</v>
       </c>
       <c r="U52" s="71" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="V52" s="36" t="s">
-        <v>402</v>
-      </c>
-      <c r="W52" s="13"/>
+        <v>397</v>
+      </c>
+      <c r="W52" s="13" t="s">
+        <v>442</v>
+      </c>
       <c r="X52" s="13"/>
       <c r="Y52" s="13"/>
       <c r="Z52" s="37"/>
-      <c r="AA52" s="36"/>
+      <c r="AA52" s="36" t="s">
+        <v>399</v>
+      </c>
       <c r="AB52" s="13" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AC52" s="13" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="AD52" s="13" t="s">
-        <v>401</v>
-      </c>
-      <c r="AE52" s="37"/>
+        <v>396</v>
+      </c>
+      <c r="AE52" s="37" t="s">
+        <v>396</v>
+      </c>
     </row>
     <row r="53" spans="1:31" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="31" t="s">
@@ -6804,24 +6859,30 @@
       <c r="J53" s="12"/>
       <c r="K53" s="41"/>
       <c r="L53" s="36"/>
-      <c r="M53" s="13"/>
-      <c r="N53" s="13"/>
+      <c r="M53" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="N53" s="13" t="s">
+        <v>227</v>
+      </c>
       <c r="O53" s="13"/>
       <c r="P53" s="37"/>
       <c r="Q53" s="36"/>
       <c r="R53" s="13"/>
       <c r="S53" s="13"/>
-      <c r="T53" s="13"/>
+      <c r="T53" s="13" t="s">
+        <v>228</v>
+      </c>
       <c r="U53" s="71" t="s">
         <v>228</v>
       </c>
       <c r="V53" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="W53" s="13" t="s">
+      <c r="W53" s="13"/>
+      <c r="X53" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X53" s="13"/>
       <c r="Y53" s="13" t="s">
         <v>223</v>
       </c>
@@ -6860,18 +6921,24 @@
       <c r="K54" s="41" t="s">
         <v>230</v>
       </c>
-      <c r="L54" s="36"/>
+      <c r="L54" s="36" t="s">
+        <v>443</v>
+      </c>
       <c r="M54" s="13" t="s">
-        <v>420</v>
-      </c>
-      <c r="N54" s="13"/>
-      <c r="O54" s="13"/>
+        <v>415</v>
+      </c>
+      <c r="N54" s="13" t="s">
+        <v>400</v>
+      </c>
+      <c r="O54" s="13" t="s">
+        <v>231</v>
+      </c>
       <c r="P54" s="37"/>
       <c r="Q54" s="36" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="R54" s="13" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="S54" s="13" t="s">
         <v>229</v>
@@ -6879,7 +6946,9 @@
       <c r="T54" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="U54" s="71"/>
+      <c r="U54" s="71" t="s">
+        <v>444</v>
+      </c>
       <c r="V54" s="36"/>
       <c r="W54" s="13"/>
       <c r="X54" s="13"/>
@@ -6902,22 +6971,34 @@
       <c r="F55" s="37"/>
       <c r="G55" s="40"/>
       <c r="H55" s="12" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="J55" s="12"/>
       <c r="K55" s="41"/>
       <c r="L55" s="36"/>
       <c r="M55" s="13"/>
       <c r="N55" s="13"/>
-      <c r="O55" s="13"/>
-      <c r="P55" s="37"/>
-      <c r="Q55" s="36"/>
-      <c r="R55" s="13"/>
-      <c r="S55" s="13"/>
-      <c r="T55" s="13"/>
+      <c r="O55" s="13" t="s">
+        <v>445</v>
+      </c>
+      <c r="P55" s="37" t="s">
+        <v>446</v>
+      </c>
+      <c r="Q55" s="36" t="s">
+        <v>447</v>
+      </c>
+      <c r="R55" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="S55" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="T55" s="13" t="s">
+        <v>448</v>
+      </c>
       <c r="U55" s="71"/>
       <c r="V55" s="36"/>
       <c r="W55" s="13"/>
@@ -6956,7 +7037,9 @@
       <c r="O56" s="13"/>
       <c r="P56" s="37"/>
       <c r="Q56" s="36"/>
-      <c r="R56" s="13"/>
+      <c r="R56" s="13" t="s">
+        <v>235</v>
+      </c>
       <c r="S56" s="13"/>
       <c r="T56" s="18"/>
       <c r="U56" s="71" t="s">
@@ -6965,16 +7048,16 @@
       <c r="V56" s="36"/>
       <c r="W56" s="13"/>
       <c r="X56" s="13"/>
-      <c r="Y56" s="13"/>
+      <c r="Y56" s="13" t="s">
+        <v>232</v>
+      </c>
       <c r="Z56" s="37" t="s">
         <v>234</v>
       </c>
       <c r="AA56" s="36"/>
-      <c r="AB56" s="13" t="s">
-        <v>232</v>
-      </c>
+      <c r="AB56" s="13"/>
       <c r="AC56" s="13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AD56" s="13" t="s">
         <v>234</v>
@@ -6999,7 +7082,7 @@
       <c r="I57" s="12"/>
       <c r="J57" s="12"/>
       <c r="K57" s="41" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L57" s="36" t="s">
         <v>236</v>
@@ -7010,10 +7093,10 @@
       <c r="N57" s="13" t="s">
         <v>247</v>
       </c>
-      <c r="O57" s="13" t="s">
+      <c r="O57" s="13"/>
+      <c r="P57" s="37" t="s">
         <v>237</v>
       </c>
-      <c r="P57" s="37"/>
       <c r="Q57" s="36"/>
       <c r="R57" s="13"/>
       <c r="S57" s="13"/>
@@ -7052,10 +7135,18 @@
       <c r="I58" s="12"/>
       <c r="J58" s="12"/>
       <c r="K58" s="41"/>
-      <c r="L58" s="36"/>
-      <c r="M58" s="13"/>
-      <c r="N58" s="13"/>
-      <c r="O58" s="13"/>
+      <c r="L58" s="36" t="s">
+        <v>242</v>
+      </c>
+      <c r="M58" s="13" t="s">
+        <v>239</v>
+      </c>
+      <c r="N58" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="O58" s="13" t="s">
+        <v>238</v>
+      </c>
       <c r="P58" s="37" t="s">
         <v>245</v>
       </c>
@@ -7063,9 +7154,7 @@
       <c r="R58" s="13"/>
       <c r="S58" s="13"/>
       <c r="T58" s="13"/>
-      <c r="U58" s="73" t="s">
-        <v>240</v>
-      </c>
+      <c r="U58" s="73"/>
       <c r="V58" s="36" t="s">
         <v>241</v>
       </c>
@@ -7081,18 +7170,10 @@
       <c r="Z58" s="37" t="s">
         <v>242</v>
       </c>
-      <c r="AA58" s="36" t="s">
-        <v>242</v>
-      </c>
-      <c r="AB58" s="10" t="s">
-        <v>240</v>
-      </c>
-      <c r="AC58" s="10" t="s">
-        <v>239</v>
-      </c>
-      <c r="AD58" s="6" t="s">
-        <v>238</v>
-      </c>
+      <c r="AA58" s="36"/>
+      <c r="AB58" s="10"/>
+      <c r="AC58" s="10"/>
+      <c r="AD58" s="6"/>
       <c r="AE58" s="37"/>
     </row>
     <row r="59" spans="1:31" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7148,13 +7229,13 @@
       <c r="K60" s="41"/>
       <c r="L60" s="36"/>
       <c r="M60" s="13"/>
-      <c r="N60" s="13" t="s">
-        <v>249</v>
-      </c>
+      <c r="N60" s="13"/>
       <c r="O60" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="P60" s="37"/>
+      <c r="P60" s="37" t="s">
+        <v>249</v>
+      </c>
       <c r="Q60" s="36" t="s">
         <v>249</v>
       </c>
@@ -7192,10 +7273,10 @@
         <v>251</v>
       </c>
       <c r="H61" s="12" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="I61" s="12" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="J61" s="12" t="s">
         <v>252</v>
@@ -7216,7 +7297,7 @@
         <v>252</v>
       </c>
       <c r="P61" s="37" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="Q61" s="36"/>
       <c r="R61" s="13"/>
@@ -7245,7 +7326,7 @@
         <v>253</v>
       </c>
       <c r="F62" s="37" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="G62" s="40"/>
       <c r="H62" s="12"/>
@@ -7283,7 +7364,9 @@
       </c>
       <c r="AC62" s="13"/>
       <c r="AD62" s="13"/>
-      <c r="AE62" s="37"/>
+      <c r="AE62" s="37" t="s">
+        <v>403</v>
+      </c>
     </row>
     <row r="63" spans="1:31" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="31" t="s">
@@ -7351,12 +7434,8 @@
       <c r="L64" s="43" t="s">
         <v>258</v>
       </c>
-      <c r="M64" s="25" t="s">
-        <v>270</v>
-      </c>
-      <c r="N64" s="25" t="s">
-        <v>270</v>
-      </c>
+      <c r="M64" s="25"/>
+      <c r="N64" s="25"/>
       <c r="O64" s="25" t="s">
         <v>256</v>
       </c>
@@ -7366,8 +7445,12 @@
       <c r="Q64" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="R64" s="25"/>
-      <c r="S64" s="27"/>
+      <c r="R64" s="25" t="s">
+        <v>270</v>
+      </c>
+      <c r="S64" s="27" t="s">
+        <v>270</v>
+      </c>
       <c r="T64" s="45" t="s">
         <v>258</v>
       </c>
@@ -7413,19 +7496,19 @@
         <v>261</v>
       </c>
       <c r="K65" s="46"/>
-      <c r="L65" s="43"/>
+      <c r="L65" s="43" t="s">
+        <v>261</v>
+      </c>
       <c r="M65" s="25" t="s">
         <v>261</v>
       </c>
       <c r="N65" s="25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="O65" s="25" t="s">
         <v>265</v>
       </c>
-      <c r="P65" s="44" t="s">
-        <v>265</v>
-      </c>
+      <c r="P65" s="44"/>
       <c r="Q65" s="43" t="s">
         <v>263</v>
       </c>
@@ -7483,13 +7566,13 @@
         <v>268</v>
       </c>
       <c r="L66" s="58"/>
-      <c r="M66" s="26" t="s">
-        <v>267</v>
-      </c>
+      <c r="M66" s="26"/>
       <c r="N66" s="26" t="s">
         <v>267</v>
       </c>
-      <c r="O66" s="26"/>
+      <c r="O66" s="26" t="s">
+        <v>267</v>
+      </c>
       <c r="P66" s="46" t="s">
         <v>266</v>
       </c>
@@ -7587,7 +7670,9 @@
       <c r="P68" s="44" t="s">
         <v>274</v>
       </c>
-      <c r="Q68" s="43"/>
+      <c r="Q68" s="43" t="s">
+        <v>276</v>
+      </c>
       <c r="R68" s="25" t="s">
         <v>273</v>
       </c>
@@ -7597,10 +7682,10 @@
       <c r="T68" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="U68" s="75" t="s">
-        <v>276</v>
-      </c>
-      <c r="V68" s="43"/>
+      <c r="U68" s="75"/>
+      <c r="V68" s="43" t="s">
+        <v>274</v>
+      </c>
       <c r="W68" s="25" t="s">
         <v>272</v>
       </c>
@@ -7608,12 +7693,8 @@
         <v>272</v>
       </c>
       <c r="Y68" s="25"/>
-      <c r="Z68" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="AA68" s="43" t="s">
-        <v>272</v>
-      </c>
+      <c r="Z68" s="44"/>
+      <c r="AA68" s="43"/>
       <c r="AB68" s="25"/>
       <c r="AC68" s="25"/>
       <c r="AD68" s="25" t="s">
@@ -7645,16 +7726,14 @@
       </c>
       <c r="J69" s="26"/>
       <c r="K69" s="46"/>
-      <c r="L69" s="43" t="s">
-        <v>278</v>
-      </c>
+      <c r="L69" s="43"/>
       <c r="M69" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="N69" s="25"/>
-      <c r="O69" s="25" t="s">
-        <v>279</v>
-      </c>
+      <c r="N69" s="25" t="s">
+        <v>278</v>
+      </c>
+      <c r="O69" s="25"/>
       <c r="P69" s="44" t="s">
         <v>257</v>
       </c>
@@ -7676,8 +7755,12 @@
         <v>257</v>
       </c>
       <c r="X69" s="25"/>
-      <c r="Y69" s="25"/>
-      <c r="Z69" s="44"/>
+      <c r="Y69" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="Z69" s="44" t="s">
+        <v>277</v>
+      </c>
       <c r="AA69" s="43" t="s">
         <v>277</v>
       </c>
@@ -7687,7 +7770,9 @@
       <c r="AC69" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="AD69" s="25"/>
+      <c r="AD69" s="25" t="s">
+        <v>279</v>
+      </c>
       <c r="AE69" s="81"/>
     </row>
     <row r="70" spans="1:33" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -7712,9 +7797,7 @@
       </c>
       <c r="J70" s="26"/>
       <c r="K70" s="46"/>
-      <c r="L70" s="43" t="s">
-        <v>282</v>
-      </c>
+      <c r="L70" s="43"/>
       <c r="M70" s="25" t="s">
         <v>281</v>
       </c>
@@ -7725,11 +7808,15 @@
         <v>280</v>
       </c>
       <c r="P70" s="44"/>
-      <c r="Q70" s="43"/>
-      <c r="R70" s="25"/>
+      <c r="Q70" s="43" t="s">
+        <v>282</v>
+      </c>
+      <c r="R70" s="25" t="s">
+        <v>282</v>
+      </c>
       <c r="S70" s="25"/>
       <c r="T70" s="25" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U70" s="77"/>
       <c r="V70" s="43" t="s">
@@ -7741,23 +7828,23 @@
       <c r="X70" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="Y70" s="25" t="s">
+      <c r="Y70" s="25"/>
+      <c r="Z70" s="44" t="s">
         <v>282</v>
       </c>
-      <c r="Z70" s="44"/>
       <c r="AA70" s="43" t="s">
         <v>280</v>
       </c>
       <c r="AB70" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="AC70" s="25" t="s">
-        <v>281</v>
-      </c>
+      <c r="AC70" s="25"/>
       <c r="AD70" s="25" t="s">
         <v>283</v>
       </c>
-      <c r="AE70" s="81"/>
+      <c r="AE70" s="81" t="s">
+        <v>282</v>
+      </c>
     </row>
     <row r="71" spans="1:33" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="31" t="s">
@@ -7794,9 +7881,7 @@
         <v>269</v>
       </c>
       <c r="N71" s="25"/>
-      <c r="O71" s="25" t="s">
-        <v>284</v>
-      </c>
+      <c r="O71" s="25"/>
       <c r="P71" s="44" t="s">
         <v>284</v>
       </c>
@@ -7807,13 +7892,13 @@
         <v>285</v>
       </c>
       <c r="S71" s="25"/>
-      <c r="T71" s="25" t="s">
-        <v>264</v>
-      </c>
+      <c r="T71" s="25"/>
       <c r="U71" s="77" t="s">
         <v>264</v>
       </c>
-      <c r="V71" s="43"/>
+      <c r="V71" s="43" t="s">
+        <v>284</v>
+      </c>
       <c r="W71" s="25"/>
       <c r="X71" s="25" t="s">
         <v>264</v>
@@ -7829,8 +7914,12 @@
       </c>
       <c r="AB71" s="25"/>
       <c r="AC71" s="45"/>
-      <c r="AD71" s="25"/>
-      <c r="AE71" s="44"/>
+      <c r="AD71" s="25" t="s">
+        <v>285</v>
+      </c>
+      <c r="AE71" s="44" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="72" spans="1:33" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="31" t="s">
@@ -7869,7 +7958,7 @@
     </row>
     <row r="73" spans="1:33" ht="18.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="31" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
       <c r="B73" s="43"/>
       <c r="C73" s="25"/>
@@ -7930,9 +8019,7 @@
       <c r="Q74" s="43"/>
       <c r="R74" s="25"/>
       <c r="S74" s="25"/>
-      <c r="T74" s="25" t="s">
-        <v>286</v>
-      </c>
+      <c r="T74" s="25"/>
       <c r="U74" s="75" t="s">
         <v>286</v>
       </c>
@@ -7944,8 +8031,12 @@
       <c r="AA74" s="43" t="s">
         <v>287</v>
       </c>
-      <c r="AB74" s="25"/>
-      <c r="AC74" s="25"/>
+      <c r="AB74" s="25" t="s">
+        <v>286</v>
+      </c>
+      <c r="AC74" s="25" t="s">
+        <v>286</v>
+      </c>
       <c r="AD74" s="25"/>
       <c r="AE74" s="44"/>
     </row>
@@ -7974,39 +8065,43 @@
         <v>294</v>
       </c>
       <c r="N75" s="26"/>
-      <c r="O75" s="26"/>
-      <c r="P75" s="46" t="s">
+      <c r="O75" s="26" t="s">
         <v>290</v>
       </c>
+      <c r="P75" s="46"/>
       <c r="Q75" s="43" t="s">
         <v>289</v>
       </c>
       <c r="R75" s="25" t="s">
         <v>289</v>
       </c>
-      <c r="S75" s="25"/>
+      <c r="S75" s="25" t="s">
+        <v>291</v>
+      </c>
       <c r="T75" s="25"/>
       <c r="U75" s="75"/>
       <c r="V75" s="43" t="s">
         <v>290</v>
       </c>
-      <c r="W75" s="25"/>
-      <c r="X75" s="25" t="s">
+      <c r="W75" s="25" t="s">
         <v>291</v>
       </c>
+      <c r="X75" s="25"/>
       <c r="Y75" s="25"/>
-      <c r="Z75" s="44" t="s">
+      <c r="Z75" s="44"/>
+      <c r="AA75" s="43" t="s">
         <v>289</v>
       </c>
-      <c r="AA75" s="43"/>
       <c r="AB75" s="25" t="s">
+        <v>289</v>
+      </c>
+      <c r="AC75" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="AC75" s="25" t="s">
+      <c r="AD75" s="25"/>
+      <c r="AE75" s="44" t="s">
         <v>292</v>
       </c>
-      <c r="AD75" s="25"/>
-      <c r="AE75" s="44"/>
     </row>
     <row r="76" spans="1:33" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="31" t="s">
@@ -8026,7 +8121,7 @@
         <v>293</v>
       </c>
       <c r="I76" s="26" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="J76" s="26"/>
       <c r="K76" s="46" t="s">
@@ -8036,19 +8131,19 @@
         <v>293</v>
       </c>
       <c r="M76" s="25" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="N76" s="25"/>
-      <c r="O76" s="25" t="s">
-        <v>295</v>
-      </c>
+      <c r="O76" s="25"/>
       <c r="P76" s="44"/>
       <c r="Q76" s="43"/>
       <c r="R76" s="25"/>
       <c r="S76" s="25" t="s">
+        <v>295</v>
+      </c>
+      <c r="T76" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="T76" s="25"/>
       <c r="U76" s="75"/>
       <c r="V76" s="43"/>
       <c r="W76" s="25"/>
@@ -8056,11 +8151,13 @@
         <v>299</v>
       </c>
       <c r="Y76" s="25"/>
-      <c r="Z76" s="44"/>
+      <c r="Z76" s="44" t="s">
+        <v>295</v>
+      </c>
       <c r="AA76" s="43"/>
       <c r="AB76" s="25"/>
       <c r="AC76" s="25" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="AD76" s="25" t="s">
         <v>288</v>
@@ -8109,18 +8206,16 @@
       <c r="Y77" s="25" t="s">
         <v>298</v>
       </c>
-      <c r="Z77" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="AA77" s="43" t="s">
-        <v>298</v>
-      </c>
+      <c r="Z77" s="44"/>
+      <c r="AA77" s="43"/>
       <c r="AB77" s="25"/>
       <c r="AC77" s="25"/>
       <c r="AD77" s="25" t="s">
         <v>296</v>
       </c>
-      <c r="AE77" s="44"/>
+      <c r="AE77" s="44" t="s">
+        <v>298</v>
+      </c>
     </row>
     <row r="78" spans="1:33" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="31" t="s">
@@ -8163,9 +8258,7 @@
       <c r="R78" s="25" t="s">
         <v>305</v>
       </c>
-      <c r="S78" s="25" t="s">
-        <v>300</v>
-      </c>
+      <c r="S78" s="25"/>
       <c r="T78" s="25"/>
       <c r="U78" s="75"/>
       <c r="V78" s="43"/>
@@ -8179,11 +8272,9 @@
         <v>300</v>
       </c>
       <c r="Z78" s="44" t="s">
-        <v>304</v>
-      </c>
-      <c r="AA78" s="43" t="s">
-        <v>311</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="AA78" s="43"/>
       <c r="AB78" s="25"/>
       <c r="AC78" s="25" t="s">
         <v>301</v>
@@ -8191,7 +8282,9 @@
       <c r="AD78" s="25" t="s">
         <v>302</v>
       </c>
-      <c r="AE78" s="44"/>
+      <c r="AE78" s="44" t="s">
+        <v>304</v>
+      </c>
       <c r="AF78" s="6"/>
       <c r="AG78" s="6"/>
     </row>
@@ -8221,9 +8314,7 @@
       <c r="Q79" s="43"/>
       <c r="R79" s="25"/>
       <c r="S79" s="25"/>
-      <c r="T79" s="25" t="s">
-        <v>307</v>
-      </c>
+      <c r="T79" s="25"/>
       <c r="U79" s="75" t="s">
         <v>307</v>
       </c>
@@ -8233,7 +8324,9 @@
       <c r="Y79" s="25"/>
       <c r="Z79" s="44"/>
       <c r="AA79" s="43"/>
-      <c r="AB79" s="25"/>
+      <c r="AB79" s="25" t="s">
+        <v>307</v>
+      </c>
       <c r="AC79" s="25"/>
       <c r="AD79" s="25"/>
       <c r="AE79" s="44"/>
@@ -8272,16 +8365,16 @@
       <c r="O80" s="25" t="s">
         <v>306</v>
       </c>
-      <c r="P80" s="44" t="s">
-        <v>308</v>
-      </c>
+      <c r="P80" s="44"/>
       <c r="Q80" s="43"/>
       <c r="R80" s="25"/>
       <c r="S80" s="25" t="s">
         <v>306</v>
       </c>
       <c r="T80" s="25"/>
-      <c r="U80" s="75"/>
+      <c r="U80" s="75" t="s">
+        <v>309</v>
+      </c>
       <c r="V80" s="43" t="s">
         <v>306</v>
       </c>
@@ -8293,7 +8386,7 @@
       </c>
       <c r="Y80" s="45"/>
       <c r="Z80" s="44" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AA80" s="82"/>
       <c r="AB80" s="25"/>
@@ -8328,9 +8421,7 @@
       </c>
       <c r="M81" s="25"/>
       <c r="N81" s="25"/>
-      <c r="O81" s="25" t="s">
-        <v>315</v>
-      </c>
+      <c r="O81" s="25"/>
       <c r="P81" s="44"/>
       <c r="Q81" s="43" t="s">
         <v>315</v>
@@ -8354,9 +8445,7 @@
       <c r="X81" s="25" t="s">
         <v>316</v>
       </c>
-      <c r="Y81" s="25" t="s">
-        <v>315</v>
-      </c>
+      <c r="Y81" s="25"/>
       <c r="Z81" s="44" t="s">
         <v>315</v>
       </c>
@@ -8400,9 +8489,7 @@
       <c r="S82" s="84" t="s">
         <v>317</v>
       </c>
-      <c r="T82" s="84" t="s">
-        <v>318</v>
-      </c>
+      <c r="T82" s="84"/>
       <c r="U82" s="90"/>
       <c r="V82" s="89"/>
       <c r="W82" s="84" t="s">
@@ -8411,13 +8498,13 @@
       <c r="X82" s="84" t="s">
         <v>320</v>
       </c>
-      <c r="Y82" s="84" t="s">
-        <v>321</v>
-      </c>
+      <c r="Y82" s="84"/>
       <c r="Z82" s="85"/>
       <c r="AA82" s="89"/>
       <c r="AB82" s="84"/>
-      <c r="AC82" s="84"/>
+      <c r="AC82" s="84" t="s">
+        <v>321</v>
+      </c>
       <c r="AD82" s="84"/>
       <c r="AE82" s="85"/>
       <c r="AF82" s="6"/>
@@ -8447,23 +8534,27 @@
       <c r="K83" s="46" t="s">
         <v>327</v>
       </c>
-      <c r="L83" s="43"/>
+      <c r="L83" s="43" t="s">
+        <v>322</v>
+      </c>
       <c r="M83" s="25"/>
-      <c r="N83" s="25" t="s">
-        <v>329</v>
-      </c>
+      <c r="N83" s="25"/>
       <c r="O83" s="25"/>
       <c r="P83" s="44" t="s">
         <v>326</v>
       </c>
       <c r="Q83" s="43" t="s">
+        <v>329</v>
+      </c>
+      <c r="R83" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="R83" s="25"/>
       <c r="S83" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="T83" s="25"/>
+      <c r="T83" s="25" t="s">
+        <v>324</v>
+      </c>
       <c r="U83" s="75" t="s">
         <v>326</v>
       </c>
@@ -8473,20 +8564,18 @@
       <c r="W83" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="X83" s="25" t="s">
-        <v>327</v>
-      </c>
+      <c r="X83" s="25"/>
       <c r="Y83" s="25" t="s">
         <v>323</v>
       </c>
       <c r="Z83" s="44" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="AA83" s="43" t="s">
         <v>322</v>
       </c>
       <c r="AB83" s="25" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AC83" s="25" t="s">
         <v>324</v>
@@ -8494,7 +8583,9 @@
       <c r="AD83" s="25" t="s">
         <v>325</v>
       </c>
-      <c r="AE83" s="44"/>
+      <c r="AE83" s="44" t="s">
+        <v>330</v>
+      </c>
       <c r="AF83" s="6"/>
       <c r="AG83" s="6"/>
     </row>
@@ -8522,9 +8613,7 @@
       <c r="M84" s="29"/>
       <c r="N84" s="29"/>
       <c r="O84" s="29"/>
-      <c r="P84" s="48" t="s">
-        <v>332</v>
-      </c>
+      <c r="P84" s="48"/>
       <c r="Q84" s="47" t="s">
         <v>336</v>
       </c>
@@ -8532,28 +8621,38 @@
         <v>333</v>
       </c>
       <c r="S84" s="29"/>
-      <c r="T84" s="29"/>
-      <c r="U84" s="78"/>
+      <c r="T84" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="U84" s="78" t="s">
+        <v>332</v>
+      </c>
       <c r="V84" s="47" t="s">
         <v>332</v>
       </c>
-      <c r="W84" s="29"/>
+      <c r="W84" s="29" t="s">
+        <v>331</v>
+      </c>
       <c r="X84" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="Y84" s="29" t="s">
-        <v>333</v>
-      </c>
+      <c r="Y84" s="29"/>
       <c r="Z84" s="48"/>
       <c r="AA84" s="47" t="s">
         <v>334</v>
       </c>
-      <c r="AB84" s="29"/>
-      <c r="AC84" s="29"/>
+      <c r="AB84" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="AC84" s="29" t="s">
+        <v>333</v>
+      </c>
       <c r="AD84" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="AE84" s="48"/>
+        <v>333</v>
+      </c>
+      <c r="AE84" s="48" t="s">
+        <v>336</v>
+      </c>
       <c r="AF84" s="6"/>
       <c r="AG84" s="6"/>
     </row>
@@ -8578,11 +8677,15 @@
       <c r="L85" s="49" t="s">
         <v>337</v>
       </c>
-      <c r="M85" s="27"/>
+      <c r="M85" s="27" t="s">
+        <v>343</v>
+      </c>
       <c r="N85" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="O85" s="28"/>
+      <c r="O85" s="28" t="s">
+        <v>340</v>
+      </c>
       <c r="P85" s="63"/>
       <c r="Q85" s="43" t="s">
         <v>339</v>
@@ -8597,17 +8700,17 @@
       <c r="U85" s="77"/>
       <c r="V85" s="49"/>
       <c r="W85" s="27" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
       <c r="X85" s="27" t="s">
-        <v>340</v>
-      </c>
-      <c r="Y85" s="27" t="s">
-        <v>337</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="Y85" s="27"/>
       <c r="Z85" s="50"/>
       <c r="AA85" s="49"/>
-      <c r="AB85" s="27"/>
+      <c r="AB85" s="27" t="s">
+        <v>342</v>
+      </c>
       <c r="AC85" s="27"/>
       <c r="AD85" s="27"/>
       <c r="AE85" s="50"/>
@@ -8670,8 +8773,12 @@
       </c>
       <c r="K87" s="63"/>
       <c r="L87" s="49"/>
-      <c r="M87" s="27"/>
-      <c r="N87" s="27"/>
+      <c r="M87" s="27" t="s">
+        <v>345</v>
+      </c>
+      <c r="N87" s="27" t="s">
+        <v>346</v>
+      </c>
       <c r="O87" s="28" t="s">
         <v>347</v>
       </c>
@@ -8679,32 +8786,26 @@
         <v>347</v>
       </c>
       <c r="Q87" s="43"/>
-      <c r="R87" s="27" t="s">
-        <v>344</v>
-      </c>
-      <c r="S87" s="27" t="s">
-        <v>346</v>
-      </c>
-      <c r="T87" s="27" t="s">
-        <v>348</v>
-      </c>
-      <c r="U87" s="77" t="s">
-        <v>345</v>
-      </c>
+      <c r="R87" s="27"/>
+      <c r="S87" s="27"/>
+      <c r="T87" s="27"/>
+      <c r="U87" s="77"/>
       <c r="V87" s="49" t="s">
         <v>346</v>
       </c>
-      <c r="W87" s="27"/>
-      <c r="X87" s="27"/>
+      <c r="W87" s="27" t="s">
+        <v>348</v>
+      </c>
+      <c r="X87" s="27" t="s">
+        <v>345</v>
+      </c>
       <c r="Y87" s="27" t="s">
         <v>344</v>
       </c>
       <c r="Z87" s="50" t="s">
-        <v>345</v>
-      </c>
-      <c r="AA87" s="49" t="s">
-        <v>347</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="AA87" s="49"/>
       <c r="AB87" s="27"/>
       <c r="AC87" s="27"/>
       <c r="AD87" s="27"/>
@@ -8731,10 +8832,10 @@
       </c>
       <c r="I88" s="28"/>
       <c r="J88" s="28" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="K88" s="63" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="L88" s="49" t="s">
         <v>351</v>
@@ -8742,11 +8843,15 @@
       <c r="M88" s="27" t="s">
         <v>351</v>
       </c>
-      <c r="N88" s="27"/>
-      <c r="O88" s="28"/>
+      <c r="N88" s="27" t="s">
+        <v>349</v>
+      </c>
+      <c r="O88" s="28" t="s">
+        <v>349</v>
+      </c>
       <c r="P88" s="63"/>
       <c r="Q88" s="43" t="s">
-        <v>409</v>
+        <v>350</v>
       </c>
       <c r="R88" s="27" t="s">
         <v>350</v>
@@ -8757,19 +8862,17 @@
       <c r="T88" s="27" t="s">
         <v>349</v>
       </c>
-      <c r="U88" s="77"/>
+      <c r="U88" s="77" t="s">
+        <v>404</v>
+      </c>
       <c r="V88" s="49"/>
       <c r="W88" s="27"/>
       <c r="X88" s="27"/>
       <c r="Y88" s="27"/>
       <c r="Z88" s="50"/>
       <c r="AA88" s="49"/>
-      <c r="AB88" s="27" t="s">
-        <v>349</v>
-      </c>
-      <c r="AC88" s="27" t="s">
-        <v>349</v>
-      </c>
+      <c r="AB88" s="27"/>
+      <c r="AC88" s="27"/>
       <c r="AD88" s="27"/>
       <c r="AE88" s="50"/>
       <c r="AF88" s="6"/>
@@ -8830,9 +8933,11 @@
       </c>
       <c r="J90" s="28"/>
       <c r="K90" s="63"/>
-      <c r="L90" s="49"/>
+      <c r="L90" s="49" t="s">
+        <v>353</v>
+      </c>
       <c r="M90" s="27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="N90" s="27" t="s">
         <v>355</v>
@@ -8843,7 +8948,7 @@
         <v>356</v>
       </c>
       <c r="R90" s="27" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="S90" s="27" t="s">
         <v>358</v>
@@ -8855,24 +8960,26 @@
       <c r="V90" s="49" t="s">
         <v>357</v>
       </c>
-      <c r="W90" s="27" t="s">
-        <v>355</v>
-      </c>
+      <c r="W90" s="27"/>
       <c r="X90" s="27" t="s">
         <v>358</v>
       </c>
-      <c r="Y90" s="28"/>
+      <c r="Y90" s="28" t="s">
+        <v>353</v>
+      </c>
       <c r="Z90" s="50"/>
       <c r="AA90" s="49" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="AB90" s="27" t="s">
         <v>354</v>
       </c>
       <c r="AC90" s="27" t="s">
-        <v>417</v>
-      </c>
-      <c r="AD90" s="27"/>
+        <v>412</v>
+      </c>
+      <c r="AD90" s="27" t="s">
+        <v>355</v>
+      </c>
       <c r="AE90" s="50"/>
     </row>
     <row r="91" spans="1:33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -8889,10 +8996,10 @@
       <c r="I91" s="28"/>
       <c r="J91" s="28"/>
       <c r="K91" s="63"/>
-      <c r="L91" s="49" t="s">
+      <c r="L91" s="49"/>
+      <c r="M91" s="27" t="s">
         <v>360</v>
       </c>
-      <c r="M91" s="27"/>
       <c r="N91" s="27" t="s">
         <v>352</v>
       </c>
@@ -8912,9 +9019,7 @@
         <v>360</v>
       </c>
       <c r="X91" s="27"/>
-      <c r="Y91" s="98" t="s">
-        <v>185</v>
-      </c>
+      <c r="Y91" s="98"/>
       <c r="Z91" s="50"/>
       <c r="AA91" s="49" t="s">
         <v>362</v>
@@ -8925,8 +9030,12 @@
       <c r="AC91" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="AD91" s="27"/>
-      <c r="AE91" s="50"/>
+      <c r="AD91" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="AE91" s="50" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="92" spans="1:33" ht="24.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="33" t="s">
@@ -8935,48 +9044,42 @@
       <c r="B92" s="49"/>
       <c r="C92" s="27"/>
       <c r="D92" s="27" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E92" s="27"/>
       <c r="F92" s="50" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="G92" s="49" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="H92" s="26"/>
       <c r="I92" s="28" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="J92" s="28"/>
       <c r="K92" s="63" t="s">
-        <v>365</v>
-      </c>
-      <c r="L92" s="49" t="s">
-        <v>370</v>
-      </c>
+        <v>364</v>
+      </c>
+      <c r="L92" s="49"/>
       <c r="M92" s="27"/>
       <c r="N92" s="27" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="O92" s="28" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="P92" s="63" t="s">
-        <v>364</v>
-      </c>
-      <c r="Q92" s="43" t="s">
         <v>363</v>
       </c>
-      <c r="R92" s="27" t="s">
-        <v>366</v>
-      </c>
+      <c r="Q92" s="43"/>
+      <c r="R92" s="27"/>
       <c r="S92" s="27"/>
       <c r="T92" s="27" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="U92" s="77" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="V92" s="49"/>
       <c r="W92" s="27"/>
@@ -8996,61 +9099,59 @@
       <c r="B93" s="49"/>
       <c r="C93" s="27"/>
       <c r="D93" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="E93" s="27"/>
       <c r="F93" s="50"/>
       <c r="G93" s="62" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="H93" s="26" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I93" s="28"/>
       <c r="J93" s="28"/>
       <c r="K93" s="63"/>
       <c r="L93" s="49" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="M93" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="N93" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="O93" s="28"/>
       <c r="P93" s="63" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="Q93" s="43" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="R93" s="27"/>
       <c r="S93" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="T93" s="27"/>
-      <c r="U93" s="77"/>
+      <c r="U93" s="77" t="s">
+        <v>417</v>
+      </c>
       <c r="V93" s="49"/>
-      <c r="W93" s="27" t="s">
-        <v>374</v>
-      </c>
+      <c r="W93" s="27"/>
       <c r="X93" s="27"/>
       <c r="Y93" s="27"/>
-      <c r="Z93" s="50" t="s">
-        <v>422</v>
-      </c>
+      <c r="Z93" s="50"/>
       <c r="AA93" s="49" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="AB93" s="27" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="AC93" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AD93" s="27" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="AE93" s="50"/>
     </row>
@@ -9061,56 +9162,58 @@
       <c r="B94" s="49"/>
       <c r="C94" s="27"/>
       <c r="D94" s="27" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="E94" s="27"/>
       <c r="F94" s="50"/>
       <c r="G94" s="62" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="I94" s="28" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="J94" s="28"/>
       <c r="K94" s="63"/>
       <c r="L94" s="49" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="M94" s="27"/>
       <c r="N94" s="27"/>
       <c r="O94" s="28"/>
       <c r="P94" s="63"/>
       <c r="Q94" s="43" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="R94" s="27" t="s">
-        <v>379</v>
-      </c>
-      <c r="S94" s="27"/>
+        <v>375</v>
+      </c>
+      <c r="S94" s="27" t="s">
+        <v>378</v>
+      </c>
       <c r="T94" s="27"/>
       <c r="U94" s="77"/>
       <c r="V94" s="49" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="W94" s="27" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="X94" s="27" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="Y94" s="27"/>
       <c r="Z94" s="50"/>
       <c r="AA94" s="49" t="s">
+        <v>376</v>
+      </c>
+      <c r="AB94" s="27" t="s">
         <v>380</v>
       </c>
-      <c r="AB94" s="27" t="s">
-        <v>384</v>
-      </c>
       <c r="AC94" s="27" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="AD94" s="27"/>
       <c r="AE94" s="50"/>
@@ -9122,60 +9225,44 @@
       <c r="B95" s="93"/>
       <c r="C95" s="93"/>
       <c r="D95" s="93" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="E95" s="93"/>
       <c r="F95" s="93"/>
       <c r="G95" s="94" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="H95" s="95" t="s">
+        <v>384</v>
+      </c>
+      <c r="I95" s="94" t="s">
+        <v>423</v>
+      </c>
+      <c r="J95" s="94" t="s">
+        <v>432</v>
+      </c>
+      <c r="K95" s="94"/>
+      <c r="L95" s="93"/>
+      <c r="M95" s="93"/>
+      <c r="N95" s="93"/>
+      <c r="O95" s="94"/>
+      <c r="P95" s="94" t="s">
         <v>388</v>
       </c>
-      <c r="I95" s="94" t="s">
-        <v>429</v>
-      </c>
-      <c r="J95" s="94" t="s">
-        <v>439</v>
-      </c>
-      <c r="K95" s="94"/>
-      <c r="L95" s="93" t="s">
-        <v>390</v>
-      </c>
-      <c r="M95" s="93"/>
-      <c r="N95" s="93" t="s">
-        <v>391</v>
-      </c>
-      <c r="O95" s="94"/>
-      <c r="P95" s="94"/>
-      <c r="Q95" s="96" t="s">
-        <v>373</v>
-      </c>
-      <c r="R95" s="93" t="s">
-        <v>393</v>
-      </c>
+      <c r="Q95" s="96"/>
+      <c r="R95" s="93"/>
       <c r="S95" s="93"/>
       <c r="T95" s="93"/>
       <c r="U95" s="93"/>
       <c r="V95" s="93"/>
-      <c r="W95" s="93" t="s">
-        <v>392</v>
-      </c>
+      <c r="W95" s="93"/>
       <c r="X95" s="93"/>
       <c r="Y95" s="93"/>
       <c r="Z95" s="93"/>
-      <c r="AA95" s="93" t="s">
-        <v>388</v>
-      </c>
-      <c r="AB95" s="93" t="s">
-        <v>430</v>
-      </c>
-      <c r="AC95" s="93" t="s">
-        <v>373</v>
-      </c>
-      <c r="AD95" s="93" t="s">
-        <v>423</v>
-      </c>
+      <c r="AA95" s="93"/>
+      <c r="AB95" s="93"/>
+      <c r="AC95" s="93"/>
+      <c r="AD95" s="93"/>
       <c r="AE95" s="93"/>
       <c r="AF95" s="97"/>
     </row>
